--- a/diseases/d114/2000-2004.xlsx
+++ b/diseases/d114/2000-2004.xlsx
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT14" t="n">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT20" t="n">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT38" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -17001,7 +17001,7 @@
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
@@ -26555,7 +26555,7 @@
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
@@ -28941,7 +28941,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -31710,7 +31710,7 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT157" t="n">
@@ -31949,7 +31949,7 @@
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR158" t="inlineStr">
@@ -31959,7 +31959,7 @@
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT158" t="n">
@@ -33142,7 +33142,7 @@
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
@@ -33152,7 +33152,7 @@
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -34335,7 +34335,7 @@
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
@@ -34345,7 +34345,7 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT170" t="n">
@@ -35528,7 +35528,7 @@
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
@@ -35538,7 +35538,7 @@
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT176" t="n">
@@ -36721,7 +36721,7 @@
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
@@ -36731,7 +36731,7 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -37914,7 +37914,7 @@
       </c>
       <c r="AQ188" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
@@ -37924,7 +37924,7 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT188" t="n">
@@ -39107,7 +39107,7 @@
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT194" t="n">
@@ -40300,7 +40300,7 @@
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
@@ -40310,7 +40310,7 @@
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT200" t="n">
@@ -41493,7 +41493,7 @@
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
@@ -41503,7 +41503,7 @@
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT206" t="n">
@@ -42686,7 +42686,7 @@
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR212" t="inlineStr">
@@ -42696,7 +42696,7 @@
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT212" t="n">
@@ -43879,7 +43879,7 @@
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
@@ -43889,7 +43889,7 @@
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT218" t="n">
@@ -45072,7 +45072,7 @@
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
@@ -45082,7 +45082,7 @@
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -46658,7 +46658,7 @@
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
@@ -46668,7 +46668,7 @@
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT232" t="n">
@@ -46897,7 +46897,7 @@
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
@@ -46907,7 +46907,7 @@
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT233" t="n">
@@ -48090,7 +48090,7 @@
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
@@ -48100,7 +48100,7 @@
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT239" t="n">
@@ -49283,7 +49283,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -49293,7 +49293,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -50476,7 +50476,7 @@
       </c>
       <c r="AQ251" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
@@ -50486,7 +50486,7 @@
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT251" t="n">
@@ -51669,7 +51669,7 @@
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR257" t="inlineStr">
@@ -51679,7 +51679,7 @@
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT257" t="n">
@@ -52862,7 +52862,7 @@
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR263" t="inlineStr">
@@ -52872,7 +52872,7 @@
       </c>
       <c r="AS263" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT263" t="n">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
@@ -54065,7 +54065,7 @@
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -55248,7 +55248,7 @@
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR275" t="inlineStr">
@@ -55258,7 +55258,7 @@
       </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT275" t="n">
@@ -56441,7 +56441,7 @@
       </c>
       <c r="AQ281" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR281" t="inlineStr">
@@ -56451,7 +56451,7 @@
       </c>
       <c r="AS281" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT281" t="n">
@@ -57634,7 +57634,7 @@
       </c>
       <c r="AQ287" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR287" t="inlineStr">
@@ -57644,7 +57644,7 @@
       </c>
       <c r="AS287" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT287" t="n">
@@ -58827,7 +58827,7 @@
       </c>
       <c r="AQ293" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR293" t="inlineStr">
@@ -58837,7 +58837,7 @@
       </c>
       <c r="AS293" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT293" t="n">
@@ -60020,7 +60020,7 @@
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR299" t="inlineStr">
@@ -60030,7 +60030,7 @@
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT299" t="n">
@@ -61606,7 +61606,7 @@
       </c>
       <c r="AQ307" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR307" t="inlineStr">
@@ -61616,7 +61616,7 @@
       </c>
       <c r="AS307" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT307" t="n">
@@ -61845,7 +61845,7 @@
       </c>
       <c r="AQ308" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR308" t="inlineStr">
@@ -61855,7 +61855,7 @@
       </c>
       <c r="AS308" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT308" t="n">
@@ -63038,7 +63038,7 @@
       </c>
       <c r="AQ314" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR314" t="inlineStr">
@@ -63048,7 +63048,7 @@
       </c>
       <c r="AS314" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT314" t="n">
@@ -64231,7 +64231,7 @@
       </c>
       <c r="AQ320" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR320" t="inlineStr">
@@ -64241,7 +64241,7 @@
       </c>
       <c r="AS320" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT320" t="n">
@@ -65424,7 +65424,7 @@
       </c>
       <c r="AQ326" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR326" t="inlineStr">
@@ -65434,7 +65434,7 @@
       </c>
       <c r="AS326" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT326" t="n">
@@ -66617,7 +66617,7 @@
       </c>
       <c r="AQ332" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR332" t="inlineStr">
@@ -66627,7 +66627,7 @@
       </c>
       <c r="AS332" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT332" t="n">
@@ -67810,7 +67810,7 @@
       </c>
       <c r="AQ338" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR338" t="inlineStr">
@@ -67820,7 +67820,7 @@
       </c>
       <c r="AS338" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT338" t="n">
@@ -69003,7 +69003,7 @@
       </c>
       <c r="AQ344" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR344" t="inlineStr">
@@ -69013,7 +69013,7 @@
       </c>
       <c r="AS344" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT344" t="n">
@@ -70196,7 +70196,7 @@
       </c>
       <c r="AQ350" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR350" t="inlineStr">
@@ -70206,7 +70206,7 @@
       </c>
       <c r="AS350" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT350" t="n">
@@ -71389,7 +71389,7 @@
       </c>
       <c r="AQ356" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR356" t="inlineStr">
@@ -71399,7 +71399,7 @@
       </c>
       <c r="AS356" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT356" t="n">
@@ -72582,7 +72582,7 @@
       </c>
       <c r="AQ362" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR362" t="inlineStr">
@@ -72592,7 +72592,7 @@
       </c>
       <c r="AS362" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT362" t="n">
@@ -73775,7 +73775,7 @@
       </c>
       <c r="AQ368" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR368" t="inlineStr">
@@ -73785,7 +73785,7 @@
       </c>
       <c r="AS368" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT368" t="n">
@@ -74968,7 +74968,7 @@
       </c>
       <c r="AQ374" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR374" t="inlineStr">
@@ -74978,7 +74978,7 @@
       </c>
       <c r="AS374" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_SALMONELLOSIS</t>
+          <t>SER_IS_ECDC_SALM_ANNUAL</t>
         </is>
       </c>
       <c r="AT374" t="n">

--- a/diseases/d114/2000-2004.xlsx
+++ b/diseases/d114/2000-2004.xlsx
@@ -2438,7 +2438,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20965,7 +20965,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -22158,7 +22158,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26930,7 +26930,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -29316,7 +29316,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -30509,7 +30509,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -37106,7 +37106,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -38299,7 +38299,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -40685,7 +40685,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -41878,7 +41878,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -43071,7 +43071,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -44264,7 +44264,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -45457,7 +45457,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -47282,7 +47282,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -48475,7 +48475,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -49668,7 +49668,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -50861,7 +50861,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -52054,7 +52054,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -53247,7 +53247,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -54440,7 +54440,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -55633,7 +55633,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -56826,7 +56826,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -58019,7 +58019,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -59212,7 +59212,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -60405,7 +60405,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -62230,7 +62230,7 @@
       </c>
       <c r="AM310" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN310" t="b">
@@ -63423,7 +63423,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -64616,7 +64616,7 @@
       </c>
       <c r="AM322" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN322" t="b">
@@ -65809,7 +65809,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN328" t="b">
@@ -67002,7 +67002,7 @@
       </c>
       <c r="AM334" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN334" t="b">
@@ -68195,7 +68195,7 @@
       </c>
       <c r="AM340" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN340" t="b">
@@ -69388,7 +69388,7 @@
       </c>
       <c r="AM346" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN346" t="b">
@@ -70581,7 +70581,7 @@
       </c>
       <c r="AM352" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN352" t="b">
@@ -71774,7 +71774,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN358" t="b">
@@ -72967,7 +72967,7 @@
       </c>
       <c r="AM364" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN364" t="b">
@@ -74160,7 +74160,7 @@
       </c>
       <c r="AM370" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN370" t="b">
@@ -75353,7 +75353,7 @@
       </c>
       <c r="AM376" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN376" t="b">
